--- a/4_outputs/final/Table01.xlsx
+++ b/4_outputs/final/Table01.xlsx
@@ -420,11 +420,11 @@
   <dimension ref="A1:E8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="31" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="5" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="3"/>
     <col width="5" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
+    <col width="5" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -457,22 +457,18 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>OSDG Community Dataset</t>
+          <t>OSDG</t>
         </is>
       </c>
       <c r="B2" t="inlineStr"/>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>(no SDG17)</t>
-        </is>
-      </c>
+      <c r="E2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SDG Classification Benchmark</t>
+          <t>SDGCB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr"/>
@@ -483,7 +479,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>IISD SDG Knowledge Hub</t>
+          <t>SDGKH</t>
         </is>
       </c>
       <c r="B4" t="inlineStr"/>
@@ -494,7 +490,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SDGi Corpus</t>
+          <t>SDGi</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -505,7 +501,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Aurora dataset</t>
+          <t>Aurora</t>
         </is>
       </c>
       <c r="B6" t="inlineStr"/>
@@ -516,7 +512,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Research corpus (OpenAlex)</t>
+          <t>Research (OpenAlex)</t>
         </is>
       </c>
       <c r="B7" t="inlineStr"/>
@@ -531,7 +527,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Policy corpus (3 collections)</t>
+          <t>Policy (3 Collections)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
